--- a/data/trans_orig/IQ23_R2-Dificultad-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Dificultad-trans_orig.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -761,7 +761,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -796,7 +796,7 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -905,7 +905,7 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -940,7 +940,7 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -1049,7 +1049,7 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
@@ -1084,7 +1084,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -1193,7 +1193,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1228,7 +1228,7 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -1337,7 +1337,7 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -1372,7 +1372,7 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -1678,213 +1678,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>10859</v>
+        <v>64823</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>6668</v>
+        <v>54265</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>17919</v>
+        <v>76008</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.04293344637697408</v>
+        <v>0.2562897576958817</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.02636245743343773</v>
+        <v>0.214547609837608</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.0708462054184967</v>
+        <v>0.3005097270519039</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>5571</v>
+        <v>72485</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>2381</v>
+        <v>60376</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>10645</v>
+        <v>84397</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.02318785201115341</v>
+        <v>0.3016925133598671</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.009910458006096473</v>
+        <v>0.2512937411600076</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.04430737669116443</v>
+        <v>0.3512734601751343</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>16430</v>
+        <v>137308</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>10592</v>
+        <v>121979</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>23715</v>
+        <v>155299</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.03331425040788629</v>
+        <v>0.278408008287744</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.02147647291631625</v>
+        <v>0.2473257798304265</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.04808448149005148</v>
+        <v>0.3148875054123033</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>92</v>
+        <v>251</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>64823</v>
+        <v>177247</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>54265</v>
+        <v>165223</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>76008</v>
+        <v>188408</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.2562897576958817</v>
+        <v>0.7007767959271441</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.214547609837608</v>
+        <v>0.6532402435381307</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3005097270519039</v>
+        <v>0.7449053104603323</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>72485</v>
+        <v>162205</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>60376</v>
+        <v>148726</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>84397</v>
+        <v>174124</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3016925133598671</v>
+        <v>0.6751196346289794</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.2512937411600076</v>
+        <v>0.6190173264892309</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3512734601751343</v>
+        <v>0.724728187770968</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>200</v>
+        <v>484</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>137308</v>
+        <v>339452</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>121979</v>
+        <v>321283</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>155299</v>
+        <v>356289</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.278408008287744</v>
+        <v>0.6882777413043697</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.2473257798304265</v>
+        <v>0.6514387145018028</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.3148875054123033</v>
+        <v>0.7224167646774404</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>251</v>
+        <v>15</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>177247</v>
+        <v>10859</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>165223</v>
+        <v>6668</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>188408</v>
+        <v>17919</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.7007767959271441</v>
+        <v>0.04293344637697408</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.6532402435381307</v>
+        <v>0.02636245743343773</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.7449053104603323</v>
+        <v>0.0708462054184967</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>233</v>
+        <v>8</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>162205</v>
+        <v>5571</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>148726</v>
+        <v>2381</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>174124</v>
+        <v>10645</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.6751196346289794</v>
+        <v>0.02318785201115341</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6190173264892309</v>
+        <v>0.009910458006096473</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.724728187770968</v>
+        <v>0.04430737669116443</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>484</v>
+        <v>23</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>339452</v>
+        <v>16430</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>321283</v>
+        <v>10592</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>356289</v>
+        <v>23715</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.6882777413043697</v>
+        <v>0.03331425040788629</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.6514387145018028</v>
+        <v>0.02147647291631625</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7224167646774404</v>
+        <v>0.04808448149005148</v>
       </c>
     </row>
     <row r="7">
@@ -1966,213 +1966,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4770</v>
+        <v>47007</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2020</v>
+        <v>37739</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>9457</v>
+        <v>58435</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.02173737446784586</v>
+        <v>0.2142098729677584</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.009204648471610297</v>
+        <v>0.1719748138433254</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04309488351396788</v>
+        <v>0.2662840872630843</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>9308</v>
+        <v>58562</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5320</v>
+        <v>48520</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>15667</v>
+        <v>68654</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.0424005937307223</v>
+        <v>0.2667681491042635</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.02423443198987689</v>
+        <v>0.2210264240250317</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.07136615839756691</v>
+        <v>0.3127433628583663</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>14078</v>
+        <v>105569</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>8840</v>
+        <v>92518</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>20957</v>
+        <v>120153</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.03207080486906983</v>
+        <v>0.2404936422853803</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.02013691151585078</v>
+        <v>0.2107606582287868</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.04774043867055675</v>
+        <v>0.2737157809724092</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>47007</v>
+        <v>167668</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>37739</v>
+        <v>156476</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>58435</v>
+        <v>177168</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2142098729677584</v>
+        <v>0.7640527525643958</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1719748138433254</v>
+        <v>0.7130496326222068</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.2662840872630843</v>
+        <v>0.8073442070940759</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>88</v>
+        <v>216</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>58562</v>
+        <v>151653</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>48520</v>
+        <v>139834</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>68654</v>
+        <v>161703</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2667681491042635</v>
+        <v>0.6908312571650143</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2210264240250317</v>
+        <v>0.6369906376211617</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3127433628583663</v>
+        <v>0.736609155841539</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>155</v>
+        <v>453</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>105569</v>
+        <v>319322</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>92518</v>
+        <v>303317</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>120153</v>
+        <v>332511</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2404936422853803</v>
+        <v>0.7274355528455498</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.2107606582287868</v>
+        <v>0.6909734936461795</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.2737157809724092</v>
+        <v>0.7574791780022243</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>237</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>167668</v>
+        <v>4770</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>156476</v>
+        <v>2020</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>177168</v>
+        <v>9457</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7640527525643958</v>
+        <v>0.02173737446784586</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.7130496326222068</v>
+        <v>0.009204648471610297</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.8073442070940759</v>
+        <v>0.04309488351396788</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>151653</v>
+        <v>9308</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>139834</v>
+        <v>5320</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>161703</v>
+        <v>15667</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.6908312571650143</v>
+        <v>0.0424005937307223</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6369906376211617</v>
+        <v>0.02423443198987689</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.736609155841539</v>
+        <v>0.07136615839756691</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>319322</v>
+        <v>14078</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>303317</v>
+        <v>8840</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>332511</v>
+        <v>20957</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7274355528455498</v>
+        <v>0.03207080486906983</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.6909734936461795</v>
+        <v>0.02013691151585078</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.7574791780022243</v>
+        <v>0.04774043867055675</v>
       </c>
     </row>
     <row r="11">
@@ -2254,213 +2254,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3356</v>
+        <v>41684</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1326</v>
+        <v>32705</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>7560</v>
+        <v>50349</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02121632518830309</v>
+        <v>0.2635478994586794</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.008385723141066512</v>
+        <v>0.2067796227423991</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.04779821319375115</v>
+        <v>0.3183316825651182</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1883</v>
+        <v>32012</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>586</v>
+        <v>23654</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>5780</v>
+        <v>40593</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.01235909223449147</v>
+        <v>0.210055150710046</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.003847067351660371</v>
+        <v>0.1552101746230955</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.03792752592438949</v>
+        <v>0.2663660430556465</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>5239</v>
+        <v>73696</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>2540</v>
+        <v>62676</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>9820</v>
+        <v>86821</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.01686993419840481</v>
+        <v>0.2372981211816049</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.008178252228117083</v>
+        <v>0.2018148449968412</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.03162161362840343</v>
+        <v>0.2795620967899347</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>41684</v>
+        <v>113125</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>32705</v>
+        <v>104359</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>50349</v>
+        <v>122282</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2635478994586794</v>
+        <v>0.7152357753530175</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2067796227423991</v>
+        <v>0.6598156322900823</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3183316825651182</v>
+        <v>0.7731313366836546</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>45</v>
+        <v>171</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>32012</v>
+        <v>118502</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>23654</v>
+        <v>109629</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>40593</v>
+        <v>126742</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.210055150710046</v>
+        <v>0.7775857570554626</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1552101746230955</v>
+        <v>0.7193673529084897</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2663660430556465</v>
+        <v>0.8316573030064799</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>105</v>
+        <v>336</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>73696</v>
+        <v>231626</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>62676</v>
+        <v>219078</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>86821</v>
+        <v>243222</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2372981211816049</v>
+        <v>0.7458319446199903</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2018148449968412</v>
+        <v>0.7054278260877698</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2795620967899347</v>
+        <v>0.7831707530473185</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>165</v>
+        <v>5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>113125</v>
+        <v>3356</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>104359</v>
+        <v>1326</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>122282</v>
+        <v>7560</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7152357753530175</v>
+        <v>0.02121632518830309</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6598156322900823</v>
+        <v>0.008385723141066512</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7731313366836546</v>
+        <v>0.04779821319375115</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>171</v>
+        <v>3</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>118502</v>
+        <v>1883</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>109629</v>
+        <v>586</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>126742</v>
+        <v>5780</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7775857570554626</v>
+        <v>0.01235909223449147</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7193673529084897</v>
+        <v>0.003847067351660371</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8316573030064799</v>
+        <v>0.03792752592438949</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>336</v>
+        <v>8</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>231626</v>
+        <v>5239</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>219078</v>
+        <v>2540</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>243222</v>
+        <v>9820</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7458319446199903</v>
+        <v>0.01686993419840481</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7054278260877698</v>
+        <v>0.008178252228117083</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7831707530473185</v>
+        <v>0.03162161362840343</v>
       </c>
     </row>
     <row r="15">
@@ -2542,213 +2542,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2675</v>
+        <v>29246</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>740</v>
+        <v>22141</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>6667</v>
+        <v>36871</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.02788249570180014</v>
+        <v>0.3048252608248708</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.007712273257985789</v>
+        <v>0.2307793509505637</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.0694904915044412</v>
+        <v>0.3843038495436056</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>694</v>
+        <v>14447</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>9211</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>3130</v>
+        <v>21879</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.008684314358100576</v>
+        <v>0.1808656873322455</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0</v>
+        <v>0.1153110493488493</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.0391814551294391</v>
+        <v>0.2739102557887141</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>3369</v>
+        <v>43693</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>1305</v>
+        <v>35128</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>7208</v>
+        <v>53633</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01916043717871783</v>
+        <v>0.2485083298019319</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.007423836364273406</v>
+        <v>0.1997959391813265</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.04099560195996514</v>
+        <v>0.3050454837671315</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>29246</v>
+        <v>64021</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>22141</v>
+        <v>55366</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>36871</v>
+        <v>71180</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.3048252608248708</v>
+        <v>0.667292243473329</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2307793509505637</v>
+        <v>0.5770803797333312</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3843038495436056</v>
+        <v>0.7419068222843904</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>14447</v>
+        <v>64737</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>9211</v>
+        <v>57419</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>21879</v>
+        <v>70278</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1808656873322455</v>
+        <v>0.8104499983096539</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1153110493488493</v>
+        <v>0.7188345327651446</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2739102557887141</v>
+        <v>0.8798174942244322</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>62</v>
+        <v>181</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>43693</v>
+        <v>128759</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>35128</v>
+        <v>118324</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>53633</v>
+        <v>137785</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.2485083298019319</v>
+        <v>0.7323312330193502</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.1997959391813265</v>
+        <v>0.6729815565975382</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.3050454837671315</v>
+        <v>0.7836669190425871</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64021</v>
+        <v>2675</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>55366</v>
+        <v>740</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>71180</v>
+        <v>6667</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.667292243473329</v>
+        <v>0.02788249570180014</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.5770803797333312</v>
+        <v>0.007712273257985789</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7419068222843904</v>
+        <v>0.0694904915044412</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>64737</v>
+        <v>694</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>57419</v>
+        <v>0</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>70278</v>
+        <v>3130</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.8104499983096539</v>
+        <v>0.008684314358100576</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7188345327651446</v>
+        <v>0</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.8798174942244322</v>
+        <v>0.0391814551294391</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>181</v>
+        <v>5</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>128759</v>
+        <v>3369</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>118324</v>
+        <v>1305</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>137785</v>
+        <v>7208</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.7323312330193502</v>
+        <v>0.01916043717871783</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6729815565975382</v>
+        <v>0.007423836364273406</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7836669190425871</v>
+        <v>0.04099560195996514</v>
       </c>
     </row>
     <row r="19">
@@ -2830,213 +2830,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>31</v>
+        <v>261</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>21660</v>
+        <v>182760</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>15112</v>
+        <v>162594</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>29701</v>
+        <v>202169</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.02981503928184314</v>
+        <v>0.2515688059496122</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02080163439563225</v>
+        <v>0.2238102770187884</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.04088383101379556</v>
+        <v>0.2782856031534433</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>17456</v>
+        <v>177506</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>11289</v>
+        <v>160622</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>24931</v>
+        <v>196547</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.02522359294483173</v>
+        <v>0.2564891178238071</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.01631265767918796</v>
+        <v>0.232092826455987</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.03602471491788114</v>
+        <v>0.2840021911963804</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>56</v>
+        <v>522</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>39116</v>
+        <v>360266</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>28936</v>
+        <v>331640</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>50063</v>
+        <v>387285</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.02757502255141967</v>
+        <v>0.2539692654362566</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.02039818774805804</v>
+        <v>0.2337897275323869</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.03529176179147565</v>
+        <v>0.2730166165640779</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>261</v>
+        <v>743</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>182760</v>
+        <v>522061</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>162594</v>
+        <v>501726</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>202169</v>
+        <v>543240</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2515688059496122</v>
+        <v>0.7186161547685447</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2238102770187884</v>
+        <v>0.6906254327358518</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.2782856031534433</v>
+        <v>0.7477693826732462</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>261</v>
+        <v>711</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>177506</v>
+        <v>497098</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>160622</v>
+        <v>477636</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>196547</v>
+        <v>514903</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2564891178238071</v>
+        <v>0.7182872892313611</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.232092826455987</v>
+        <v>0.6901651482943626</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.2840021911963804</v>
+        <v>0.744015439254871</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>522</v>
+        <v>1454</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>360266</v>
+        <v>1019159</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>331640</v>
+        <v>991277</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>387285</v>
+        <v>1047299</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.2539692654362566</v>
+        <v>0.7184557120123237</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2337897275323869</v>
+        <v>0.6988001101749605</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.2730166165640779</v>
+        <v>0.7382927541898089</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>743</v>
+        <v>31</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>522061</v>
+        <v>21660</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>501726</v>
+        <v>15112</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>543240</v>
+        <v>29701</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7186161547685447</v>
+        <v>0.02981503928184314</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6906254327358518</v>
+        <v>0.02080163439563225</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7477693826732462</v>
+        <v>0.04088383101379556</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>711</v>
+        <v>25</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>497098</v>
+        <v>17456</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>477636</v>
+        <v>11289</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>514903</v>
+        <v>24931</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7182872892313611</v>
+        <v>0.02522359294483173</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6901651482943626</v>
+        <v>0.01631265767918796</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.744015439254871</v>
+        <v>0.03602471491788114</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1454</v>
+        <v>56</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>1019159</v>
+        <v>39116</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>991277</v>
+        <v>28936</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>1047299</v>
+        <v>50063</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7184557120123237</v>
+        <v>0.02757502255141967</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6988001101749605</v>
+        <v>0.02039818774805804</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7382927541898089</v>
+        <v>0.03529176179147565</v>
       </c>
     </row>
     <row r="23">
@@ -3350,213 +3350,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>4243</v>
+        <v>89113</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1944</v>
+        <v>76304</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>9127</v>
+        <v>101932</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.01479328452149771</v>
+        <v>0.3106621671223626</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.006778262607431771</v>
+        <v>0.2660091114554636</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.03181973390302115</v>
+        <v>0.3553499706691703</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4697</v>
+        <v>64230</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>1881</v>
+        <v>53041</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>9699</v>
+        <v>74943</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.01799905136750886</v>
+        <v>0.2461145602828032</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.007209159894652514</v>
+        <v>0.2032376586446097</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.03716518781782204</v>
+        <v>0.2871626898693033</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>8941</v>
+        <v>153344</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>4502</v>
+        <v>134348</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>14679</v>
+        <v>170654</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.01632047125317957</v>
+        <v>0.2799125045728705</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.00821831469176719</v>
+        <v>0.2452372907681339</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.02679414464106276</v>
+        <v>0.3115104769800226</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>89113</v>
+        <v>193492</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>76304</v>
+        <v>180416</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>101932</v>
+        <v>206391</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.3106621671223626</v>
+        <v>0.6745445483561398</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2660091114554636</v>
+        <v>0.6289570524205522</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3553499706691703</v>
+        <v>0.7195103004582827</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>99</v>
+        <v>290</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>64230</v>
+        <v>192050</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>53041</v>
+        <v>180402</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>74943</v>
+        <v>202663</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2461145602828032</v>
+        <v>0.7358863883496879</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.2032376586446097</v>
+        <v>0.6912530692763004</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2871626898693033</v>
+        <v>0.7765505388031682</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>225</v>
+        <v>563</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>153344</v>
+        <v>385543</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>134348</v>
+        <v>368085</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>170654</v>
+        <v>403997</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.2799125045728705</v>
+        <v>0.70376702417395</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.2452372907681339</v>
+        <v>0.6718996888890389</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.3115104769800226</v>
+        <v>0.7374532702369562</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>273</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>193492</v>
+        <v>4243</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>180416</v>
+        <v>1944</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>206391</v>
+        <v>9127</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6745445483561398</v>
+        <v>0.01479328452149771</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.6289570524205522</v>
+        <v>0.006778262607431771</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.7195103004582827</v>
+        <v>0.03181973390302115</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>290</v>
+        <v>7</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>192050</v>
+        <v>4697</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>180402</v>
+        <v>1881</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>202663</v>
+        <v>9699</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.7358863883496879</v>
+        <v>0.01799905136750886</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6912530692763004</v>
+        <v>0.007209159894652514</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.7765505388031682</v>
+        <v>0.03716518781782204</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>563</v>
+        <v>14</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>385543</v>
+        <v>8941</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>368085</v>
+        <v>4502</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>403997</v>
+        <v>14679</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.70376702417395</v>
+        <v>0.01632047125317957</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.6718996888890389</v>
+        <v>0.00821831469176719</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7374532702369562</v>
+        <v>0.02679414464106276</v>
       </c>
     </row>
     <row r="7">
@@ -3638,213 +3638,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3246</v>
+        <v>65252</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1292</v>
+        <v>56182</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>8012</v>
+        <v>78219</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01642294935504781</v>
+        <v>0.3301619149804845</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.006538450818850193</v>
+        <v>0.2842667244817472</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.04053825763097967</v>
+        <v>0.3957692074897816</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>3480</v>
+        <v>66641</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1668</v>
+        <v>56574</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>7552</v>
+        <v>77654</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.01762854185005984</v>
+        <v>0.3376045099224481</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.008451414833770919</v>
+        <v>0.28660105931754</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.03825841463614074</v>
+        <v>0.3933924143861231</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>11</v>
+        <v>196</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>6726</v>
+        <v>131894</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>3552</v>
+        <v>117916</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>12048</v>
+        <v>147437</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01702537592034349</v>
+        <v>0.3338809302583039</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.008990953690508887</v>
+        <v>0.2984976671910435</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.03049907167150533</v>
+        <v>0.3732281742348144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>65252</v>
+        <v>129139</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>56182</v>
+        <v>116586</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>78219</v>
+        <v>138673</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.3301619149804845</v>
+        <v>0.6534151356644676</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2842667244817472</v>
+        <v>0.5898985385485125</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.3957692074897816</v>
+        <v>0.7016553115522273</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>101</v>
+        <v>189</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>66641</v>
+        <v>127274</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>56574</v>
+        <v>115692</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>77654</v>
+        <v>137703</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.3376045099224481</v>
+        <v>0.6447669482274921</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.28660105931754</v>
+        <v>0.5860948349719928</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3933924143861231</v>
+        <v>0.6975991679524622</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>196</v>
+        <v>373</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>131894</v>
+        <v>256413</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>117916</v>
+        <v>240938</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>147437</v>
+        <v>270728</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.3338809302583039</v>
+        <v>0.6490936938213526</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.2984976671910435</v>
+        <v>0.6099193576198974</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.3732281742348144</v>
+        <v>0.6853325211574725</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>184</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>129139</v>
+        <v>3246</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>116586</v>
+        <v>1292</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>138673</v>
+        <v>8012</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.6534151356644676</v>
+        <v>0.01642294935504781</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.5898985385485125</v>
+        <v>0.006538450818850193</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7016553115522273</v>
+        <v>0.04053825763097967</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>189</v>
+        <v>6</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>127274</v>
+        <v>3480</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>115692</v>
+        <v>1668</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>137703</v>
+        <v>7552</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.6447669482274921</v>
+        <v>0.01762854185005984</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.5860948349719928</v>
+        <v>0.008451414833770919</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6975991679524622</v>
+        <v>0.03825841463614074</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>373</v>
+        <v>11</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>256413</v>
+        <v>6726</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>240938</v>
+        <v>3552</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>270728</v>
+        <v>12048</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.6490936938213526</v>
+        <v>0.01702537592034349</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.6099193576198974</v>
+        <v>0.008990953690508887</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.6853325211574725</v>
+        <v>0.03049907167150533</v>
       </c>
     </row>
     <row r="11">
@@ -3926,213 +3926,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3293</v>
+        <v>52003</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1292</v>
+        <v>42911</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>7316</v>
+        <v>61876</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02232355940234136</v>
+        <v>0.3524966893457881</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.008754860897829153</v>
+        <v>0.2908657604136389</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.04958881096044891</v>
+        <v>0.4194181270377154</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1673</v>
+        <v>53421</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>498</v>
+        <v>44779</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>4387</v>
+        <v>62957</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.01096142700054948</v>
+        <v>0.3499563662122248</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.003261006231762999</v>
+        <v>0.2933449435265665</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.02874077117435696</v>
+        <v>0.4124272999184232</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>4967</v>
+        <v>105425</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>1942</v>
+        <v>91388</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>9189</v>
+        <v>118166</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.01654556226140292</v>
+        <v>0.3512048561507732</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.00647034732241891</v>
+        <v>0.3044455414565068</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.03061015470916379</v>
+        <v>0.393650193758474</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>52003</v>
+        <v>92232</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>42911</v>
+        <v>82058</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>61876</v>
+        <v>101383</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.3524966893457881</v>
+        <v>0.6251797512518705</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2908657604136389</v>
+        <v>0.5562188701525655</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4194181270377154</v>
+        <v>0.6872048744214291</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>53421</v>
+        <v>97557</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>44779</v>
+        <v>87841</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>62957</v>
+        <v>106495</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3499563662122248</v>
+        <v>0.6390822067872257</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2933449435265665</v>
+        <v>0.5754352970216735</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.4124272999184232</v>
+        <v>0.6976388043092737</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>158</v>
+        <v>276</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>105425</v>
+        <v>189789</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>91388</v>
+        <v>176503</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>118166</v>
+        <v>203326</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.3512048561507732</v>
+        <v>0.6322495815878239</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3044455414565068</v>
+        <v>0.5879912930654826</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.393650193758474</v>
+        <v>0.6773469935587063</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>133</v>
+        <v>5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>92232</v>
+        <v>3293</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>82058</v>
+        <v>1292</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>101383</v>
+        <v>7316</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6251797512518705</v>
+        <v>0.02232355940234136</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.5562188701525655</v>
+        <v>0.008754860897829153</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.6872048744214291</v>
+        <v>0.04958881096044891</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>97557</v>
+        <v>1673</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>87841</v>
+        <v>498</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>106495</v>
+        <v>4387</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6390822067872257</v>
+        <v>0.01096142700054948</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5754352970216735</v>
+        <v>0.003261006231762999</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.6976388043092737</v>
+        <v>0.02874077117435696</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>276</v>
+        <v>8</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>189789</v>
+        <v>4967</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>176503</v>
+        <v>1942</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>203326</v>
+        <v>9189</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6322495815878239</v>
+        <v>0.01654556226140292</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.5879912930654826</v>
+        <v>0.00647034732241891</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.6773469935587063</v>
+        <v>0.03061015470916379</v>
       </c>
     </row>
     <row r="15">
@@ -4214,213 +4214,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>590</v>
+        <v>24252</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>17822</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>3373</v>
+        <v>31772</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.005904422374665465</v>
+        <v>0.2425889356301955</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>0.1782690720874461</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03373714643571587</v>
+        <v>0.3178167334434117</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1706</v>
+        <v>20517</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>527</v>
+        <v>14664</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>4786</v>
+        <v>26805</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.02162826687800302</v>
+        <v>0.2601194549973906</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.006675960777852446</v>
+        <v>0.1859175457974336</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.0606803916477957</v>
+        <v>0.3398376662912805</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>2296</v>
+        <v>44769</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>618</v>
+        <v>36207</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>5930</v>
+        <v>54140</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01283904226948362</v>
+        <v>0.2503203456135773</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.003455502058792998</v>
+        <v>0.2024469094558708</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.03315789051154578</v>
+        <v>0.3027180671424811</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>24252</v>
+        <v>75128</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>17822</v>
+        <v>67441</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>31772</v>
+        <v>81763</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.2425889356301955</v>
+        <v>0.7515066419951389</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.1782690720874461</v>
+        <v>0.6746113365318737</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3178167334434117</v>
+        <v>0.8178706914474981</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>20517</v>
+        <v>56653</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>14664</v>
+        <v>50293</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>26805</v>
+        <v>63033</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2601194549973906</v>
+        <v>0.7182522781246063</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1859175457974336</v>
+        <v>0.6376162525147058</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3398376662912805</v>
+        <v>0.7991343520154662</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>44769</v>
+        <v>131781</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>36207</v>
+        <v>121914</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>54140</v>
+        <v>140744</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.2503203456135773</v>
+        <v>0.7368406121169391</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2024469094558708</v>
+        <v>0.6816681771201947</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.3027180671424811</v>
+        <v>0.7869564392860011</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>75128</v>
+        <v>590</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>67441</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>81763</v>
+        <v>3373</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.7515066419951389</v>
+        <v>0.005904422374665465</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6746113365318737</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.8178706914474981</v>
+        <v>0.03373714643571587</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>56653</v>
+        <v>1706</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>50293</v>
+        <v>527</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>63033</v>
+        <v>4786</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.7182522781246063</v>
+        <v>0.02162826687800302</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6376162525147058</v>
+        <v>0.006675960777852446</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7991343520154662</v>
+        <v>0.0606803916477957</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>188</v>
+        <v>4</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>131781</v>
+        <v>2296</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>121914</v>
+        <v>618</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>140744</v>
+        <v>5930</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.7368406121169391</v>
+        <v>0.01283904226948362</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6816681771201947</v>
+        <v>0.003455502058792998</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7869564392860011</v>
+        <v>0.03315789051154578</v>
       </c>
     </row>
     <row r="19">
@@ -4502,213 +4502,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>18</v>
+        <v>332</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>11373</v>
+        <v>230620</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>7133</v>
+        <v>211133</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>18428</v>
+        <v>253451</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.0155370132017819</v>
+        <v>0.3150617171020342</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.009745071655591572</v>
+        <v>0.2884383216458168</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.0251748894329533</v>
+        <v>0.3462521376086045</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>19</v>
+        <v>313</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>11556</v>
+        <v>204810</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>6842</v>
+        <v>185124</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>17403</v>
+        <v>223146</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.01675077966486016</v>
+        <v>0.2968695899248456</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.009916910290367559</v>
+        <v>0.2683342867478142</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.02522507809369502</v>
+        <v>0.3234479845772675</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>37</v>
+        <v>645</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>22929</v>
+        <v>435431</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>16824</v>
+        <v>408411</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>32551</v>
+        <v>462245</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.01612593326889242</v>
+        <v>0.3062348883141456</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.01183185853058443</v>
+        <v>0.2872323573023725</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.02289287586322249</v>
+        <v>0.3250930344106777</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>332</v>
+        <v>695</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>230620</v>
+        <v>489992</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>211133</v>
+        <v>467010</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>253451</v>
+        <v>509733</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.3150617171020342</v>
+        <v>0.669401269696184</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2884383216458168</v>
+        <v>0.6380052817095508</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3462521376086045</v>
+        <v>0.6963713634248391</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>313</v>
+        <v>705</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>204810</v>
+        <v>473533</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>185124</v>
+        <v>454903</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>223146</v>
+        <v>494526</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2968695899248456</v>
+        <v>0.6863796304102943</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.2683342867478142</v>
+        <v>0.6593764746898141</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3234479845772675</v>
+        <v>0.716809717535648</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>645</v>
+        <v>1400</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>435431</v>
+        <v>963525</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>408411</v>
+        <v>935712</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>462245</v>
+        <v>991680</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.3062348883141456</v>
+        <v>0.677639178416962</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2872323573023725</v>
+        <v>0.6580785430137991</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.3250930344106777</v>
+        <v>0.6974402543878373</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>695</v>
+        <v>18</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>489992</v>
+        <v>11373</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>467010</v>
+        <v>7133</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>509733</v>
+        <v>18428</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.669401269696184</v>
+        <v>0.0155370132017819</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6380052817095508</v>
+        <v>0.009745071655591572</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.6963713634248391</v>
+        <v>0.0251748894329533</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>705</v>
+        <v>19</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>473533</v>
+        <v>11556</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>454903</v>
+        <v>6842</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>494526</v>
+        <v>17403</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.6863796304102943</v>
+        <v>0.01675077966486016</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6593764746898141</v>
+        <v>0.009916910290367559</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.716809717535648</v>
+        <v>0.02522507809369502</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1400</v>
+        <v>37</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>963525</v>
+        <v>22929</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>935712</v>
+        <v>16824</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>991680</v>
+        <v>32551</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.677639178416962</v>
+        <v>0.01612593326889242</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6580785430137991</v>
+        <v>0.01183185853058443</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.6974402543878373</v>
+        <v>0.02289287586322249</v>
       </c>
     </row>
     <row r="23">
@@ -5022,205 +5022,205 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3327</v>
+        <v>26123</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>742</v>
+        <v>19029</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>9425</v>
+        <v>33873</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.03409582673299345</v>
+        <v>0.2676979507205113</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.007598985569213783</v>
+        <v>0.1950037988192497</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.09658466134274615</v>
+        <v>0.3471181491037303</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
+        <v>26327</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>19829</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>34206</v>
+      </c>
       <c r="N4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
+        <v>0.3134972834882311</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>0.2361221325699673</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>0.4073154335841336</v>
+      </c>
       <c r="Q4" s="5" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>3327</v>
+        <v>52450</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>727</v>
+        <v>43010</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>10141</v>
+        <v>63762</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.01832542246581336</v>
+        <v>0.2888815987537508</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.004001591556294081</v>
+        <v>0.2368892720943579</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.05585403867485066</v>
+        <v>0.3511856782061578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>26123</v>
+        <v>68133</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>19029</v>
+        <v>60657</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>33873</v>
+        <v>75579</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.2676979507205113</v>
+        <v>0.6982062225464951</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.1950037988192497</v>
+        <v>0.6215910064366074</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3471181491037303</v>
+        <v>0.7745065074390879</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>26327</v>
+        <v>57651</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>19829</v>
+        <v>49772</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>34206</v>
+        <v>64149</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3134972834882311</v>
+        <v>0.6865027165117689</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.2361221325699673</v>
+        <v>0.5926845664158668</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.4073154335841336</v>
+        <v>0.7638778674300329</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>52450</v>
+        <v>125784</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>43010</v>
+        <v>114339</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>63762</v>
+        <v>135335</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.2888815987537508</v>
+        <v>0.6927929787804359</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.2368892720943579</v>
+        <v>0.629753735401646</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.3511856782061578</v>
+        <v>0.7453987490557122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>68133</v>
+        <v>3327</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>60657</v>
+        <v>742</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>75579</v>
+        <v>9425</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6982062225464951</v>
+        <v>0.03409582673299345</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.6215910064366074</v>
+        <v>0.007598985569213783</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.7745065074390879</v>
+        <v>0.09658466134274615</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>57651</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>49772</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>64149</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="6" t="n">
-        <v>0.6865027165117689</v>
-      </c>
-      <c r="O6" s="6" t="n">
-        <v>0.5926845664158668</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>0.7638778674300329</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="5" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>125784</v>
+        <v>3327</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>114339</v>
+        <v>727</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>135335</v>
+        <v>10141</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.6927929787804359</v>
+        <v>0.01832542246581336</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.629753735401646</v>
+        <v>0.004001591556294081</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7453987490557122</v>
+        <v>0.05585403867485066</v>
       </c>
     </row>
     <row r="7">
@@ -5302,213 +5302,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>669</v>
+        <v>53661</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>42736</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>3547</v>
+        <v>67180</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.003183053845526488</v>
+        <v>0.2553886794643288</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0</v>
+        <v>0.2033901522149932</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.01687886711682977</v>
+        <v>0.3197293845355096</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4020</v>
+        <v>37872</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1247</v>
+        <v>29358</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>9206</v>
+        <v>46614</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.0216474286151891</v>
+        <v>0.2039275655469071</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.006712875118975138</v>
+        <v>0.1580800829749393</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.04957210053934078</v>
+        <v>0.2509986459457508</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>6</v>
+        <v>147</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>4689</v>
+        <v>91533</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>1695</v>
+        <v>75612</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>9878</v>
+        <v>108264</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.011846075861756</v>
+        <v>0.2312444141746753</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.004282814518594468</v>
+        <v>0.1910224203717819</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.0249548783025839</v>
+        <v>0.2735122399759367</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>53661</v>
+        <v>155786</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>42736</v>
+        <v>142681</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>67180</v>
+        <v>167048</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2553886794643288</v>
+        <v>0.7414282666901446</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2033901522149932</v>
+        <v>0.6790576913152153</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.3197293845355096</v>
+        <v>0.7950275161023804</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>37872</v>
+        <v>143821</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>29358</v>
+        <v>134246</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>46614</v>
+        <v>152422</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2039275655469071</v>
+        <v>0.7744250058379042</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.1580800829749393</v>
+        <v>0.7228705710270775</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2509986459457508</v>
+        <v>0.8207390989184181</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>147</v>
+        <v>395</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>91533</v>
+        <v>299607</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>75612</v>
+        <v>283283</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>108264</v>
+        <v>315508</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2312444141746753</v>
+        <v>0.7569095099635686</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.1910224203717819</v>
+        <v>0.7156697571454163</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.2735122399759367</v>
+        <v>0.797082222765047</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>195</v>
+        <v>1</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>155786</v>
+        <v>669</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>142681</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>167048</v>
+        <v>3547</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7414282666901446</v>
+        <v>0.003183053845526488</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6790576913152153</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7950275161023804</v>
+        <v>0.01687886711682977</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>143821</v>
+        <v>4020</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>134246</v>
+        <v>1247</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>152422</v>
+        <v>9206</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7744250058379042</v>
+        <v>0.0216474286151891</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.7228705710270775</v>
+        <v>0.006712875118975138</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.8207390989184181</v>
+        <v>0.04957210053934078</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>395</v>
+        <v>6</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>299607</v>
+        <v>4689</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>283283</v>
+        <v>1695</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>315508</v>
+        <v>9878</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7569095099635686</v>
+        <v>0.011846075861756</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.7156697571454163</v>
+        <v>0.004282814518594468</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.797082222765047</v>
+        <v>0.0249548783025839</v>
       </c>
     </row>
     <row r="11">
@@ -5590,205 +5590,205 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+        <v>66596</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>56342</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>79064</v>
+      </c>
       <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
+        <v>0.2876570773000169</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.2433647640213396</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3415128563336047</v>
+      </c>
       <c r="J12" s="5" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>3392</v>
+        <v>50643</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>986</v>
+        <v>41657</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>7664</v>
+        <v>60203</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.01804494279503724</v>
+        <v>0.2694265755040862</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.005248106870250658</v>
+        <v>0.2216162015792388</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.04077569845411306</v>
+        <v>0.3202842310564038</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>5</v>
+        <v>194</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>3392</v>
+        <v>117239</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>1034</v>
+        <v>101670</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>7811</v>
+        <v>133827</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.00808588558031373</v>
+        <v>0.2794880432793527</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.002465211352454425</v>
+        <v>0.2423728729649796</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.01862052880389435</v>
+        <v>0.3190311696643193</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>66596</v>
+        <v>164915</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>56342</v>
+        <v>152447</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>79064</v>
+        <v>175169</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2876570773000169</v>
+        <v>0.712342922699983</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2433647640213396</v>
+        <v>0.6584871436663952</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3415128563336047</v>
+        <v>0.7566352359786604</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>50643</v>
+        <v>133932</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>41657</v>
+        <v>123941</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>60203</v>
+        <v>143081</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2694265755040862</v>
+        <v>0.7125284817008763</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2216162015792388</v>
+        <v>0.6593783333228289</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3202842310564038</v>
+        <v>0.7612036680578137</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>194</v>
+        <v>403</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>117239</v>
+        <v>298847</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>101670</v>
+        <v>281839</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>133827</v>
+        <v>314065</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2794880432793527</v>
+        <v>0.7124260711403336</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2423728729649796</v>
+        <v>0.6718794510138477</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3190311696643193</v>
+        <v>0.7487047924204474</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>164915</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>152447</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>175169</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="6" t="n">
-        <v>0.712342922699983</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>0.6584871436663952</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>0.7566352359786604</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="5" t="n">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>133932</v>
+        <v>3392</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>123941</v>
+        <v>986</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>143081</v>
+        <v>7664</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7125284817008763</v>
+        <v>0.01804494279503724</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6593783333228289</v>
+        <v>0.005248106870250658</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7612036680578137</v>
+        <v>0.04077569845411306</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>403</v>
+        <v>5</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>298847</v>
+        <v>3392</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>281839</v>
+        <v>1034</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>314065</v>
+        <v>7811</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7124260711403336</v>
+        <v>0.00808588558031373</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6718794510138477</v>
+        <v>0.002465211352454425</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7487047924204474</v>
+        <v>0.01862052880389435</v>
       </c>
     </row>
     <row r="15">
@@ -5870,213 +5870,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1842</v>
+        <v>44086</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>33803</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>5782</v>
+        <v>53760</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01269373905162019</v>
+        <v>0.3038438416189552</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>0.2329695051482157</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03984990174789758</v>
+        <v>0.3705182372794198</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1751</v>
+        <v>49081</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>40414</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>6005</v>
+        <v>58354</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01232743090210986</v>
+        <v>0.3455243032151629</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0</v>
+        <v>0.2845088631042539</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04227786883618535</v>
+        <v>0.4108077886955716</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>3593</v>
+        <v>93167</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>890</v>
+        <v>80804</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>9144</v>
+        <v>106611</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01251252891247033</v>
+        <v>0.324462881232941</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.003100970607844879</v>
+        <v>0.2814079684428643</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.03184583410383337</v>
+        <v>0.3712815615543582</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>44086</v>
+        <v>99167</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>33803</v>
+        <v>89047</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>53760</v>
+        <v>109390</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.3038438416189552</v>
+        <v>0.6834624193294245</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2329695051482157</v>
+        <v>0.6137130878274477</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3705182372794198</v>
+        <v>0.7539205425269789</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>49081</v>
+        <v>91216</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>40414</v>
+        <v>81443</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>58354</v>
+        <v>99867</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.3455243032151629</v>
+        <v>0.6421482658827271</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2845088631042539</v>
+        <v>0.5733508624543183</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.4108077886955716</v>
+        <v>0.7030476757531097</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>160</v>
+        <v>269</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>93167</v>
+        <v>190383</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>80804</v>
+        <v>176010</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>106611</v>
+        <v>202708</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.324462881232941</v>
+        <v>0.6630245898545887</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2814079684428643</v>
+        <v>0.6129686317087395</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.3712815615543582</v>
+        <v>0.7059464830055305</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>99167</v>
+        <v>1842</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>89047</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>109390</v>
+        <v>5782</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.6834624193294245</v>
+        <v>0.01269373905162019</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6137130878274477</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7539205425269789</v>
+        <v>0.03984990174789758</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>91216</v>
+        <v>1751</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>81443</v>
+        <v>0</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>99867</v>
+        <v>6005</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.6421482658827271</v>
+        <v>0.01232743090210986</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.5733508624543183</v>
+        <v>0</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7030476757531097</v>
+        <v>0.04227786883618535</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>269</v>
+        <v>4</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>190383</v>
+        <v>3593</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>176010</v>
+        <v>890</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>202708</v>
+        <v>9144</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.6630245898545887</v>
+        <v>0.01251252891247033</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6129686317087395</v>
+        <v>0.003100970607844879</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7059464830055305</v>
+        <v>0.03184583410383337</v>
       </c>
     </row>
     <row r="19">
@@ -6158,213 +6158,213 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>7</v>
+        <v>309</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>5838</v>
+        <v>190466</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2188</v>
+        <v>169125</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>13026</v>
+        <v>214136</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.008530976308519121</v>
+        <v>0.2783349991114826</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.003196763571827243</v>
+        <v>0.2471476691228388</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.01903584122705683</v>
+        <v>0.312924306767504</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>9163</v>
+        <v>163923</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>4723</v>
+        <v>146877</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>16172</v>
+        <v>183560</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.01527940920224607</v>
+        <v>0.2733392659496104</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.007876226391500199</v>
+        <v>0.244916005637964</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.02696694659812974</v>
+        <v>0.3060832815715991</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>19</v>
+        <v>589</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>15001</v>
+        <v>354389</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>9665</v>
+        <v>327379</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>23756</v>
+        <v>384588</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.01168287387745706</v>
+        <v>0.276001710856871</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.00752684122010039</v>
+        <v>0.2549662436508469</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.01850109898412328</v>
+        <v>0.2995211857611011</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>309</v>
+        <v>639</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>190466</v>
+        <v>488002</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>169125</v>
+        <v>464894</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>214136</v>
+        <v>509384</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2783349991114826</v>
+        <v>0.7131340245799982</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2471476691228388</v>
+        <v>0.6793651726373114</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.312924306767504</v>
+        <v>0.7443809985847721</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>280</v>
+        <v>607</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>163923</v>
+        <v>426619</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>146877</v>
+        <v>406327</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>183560</v>
+        <v>444771</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.2733392659496104</v>
+        <v>0.7113813248481434</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.244916005637964</v>
+        <v>0.6775455916534825</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.3060832815715991</v>
+        <v>0.7416489994748092</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>589</v>
+        <v>1246</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>354389</v>
+        <v>914621</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>327379</v>
+        <v>885312</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>384588</v>
+        <v>942235</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>0.276001710856871</v>
+        <v>0.7123154152656719</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0.2549662436508469</v>
+        <v>0.6894897050089815</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>0.2995211857611011</v>
+        <v>0.7338212098974592</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>639</v>
+        <v>7</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>488002</v>
+        <v>5838</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>464894</v>
+        <v>2188</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>509384</v>
+        <v>13026</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.7131340245799982</v>
+        <v>0.008530976308519121</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6793651726373114</v>
+        <v>0.003196763571827243</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.7443809985847721</v>
+        <v>0.01903584122705683</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>607</v>
+        <v>12</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>426619</v>
+        <v>9163</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>406327</v>
+        <v>4723</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>444771</v>
+        <v>16172</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.7113813248481434</v>
+        <v>0.01527940920224607</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6775455916534825</v>
+        <v>0.007876226391500199</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.7416489994748092</v>
+        <v>0.02696694659812974</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1246</v>
+        <v>19</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>914621</v>
+        <v>15001</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>885312</v>
+        <v>9665</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>942235</v>
+        <v>23756</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.7123154152656719</v>
+        <v>0.01168287387745706</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.6894897050089815</v>
+        <v>0.00752684122010039</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.7338212098974592</v>
+        <v>0.01850109898412328</v>
       </c>
     </row>
     <row r="23">
